--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.37562319705872</v>
+        <v>7.698538769522043</v>
       </c>
       <c r="D2" t="n">
-        <v>45.72724527136363</v>
+        <v>7.43067735659659</v>
       </c>
       <c r="E2" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F2" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.77554106886001</v>
+        <v>7.276025423689751</v>
       </c>
       <c r="D3" t="n">
-        <v>42.76977483149267</v>
+        <v>6.950088410117559</v>
       </c>
       <c r="E3" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F3" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.03850260604151</v>
+        <v>6.831256673481746</v>
       </c>
       <c r="D4" t="n">
-        <v>40.2678035901228</v>
+        <v>6.543518083394955</v>
       </c>
       <c r="E4" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F4" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.1481599456567</v>
+        <v>9.286575991169213</v>
       </c>
       <c r="D5" t="n">
-        <v>55.35935871062244</v>
+        <v>8.995895790476148</v>
       </c>
       <c r="E5" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F5" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.81959634303851</v>
+        <v>7.283184405743758</v>
       </c>
       <c r="D6" t="n">
-        <v>42.830356439003</v>
+        <v>6.959932921337987</v>
       </c>
       <c r="E6" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F6" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.90302905338235</v>
+        <v>8.596742221174633</v>
       </c>
       <c r="D7" t="n">
-        <v>52.4923270942755</v>
+        <v>8.53000315281977</v>
       </c>
       <c r="E7" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F7" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19506547841446</v>
+        <v>3.60669814024235</v>
       </c>
       <c r="D8" t="n">
-        <v>20.23767978483009</v>
+        <v>3.288622965034889</v>
       </c>
       <c r="E8" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F8" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.99732176936708</v>
+        <v>6.17456478752215</v>
       </c>
       <c r="D9" t="n">
-        <v>37.23600754113399</v>
+        <v>6.050851225434275</v>
       </c>
       <c r="E9" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F9" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.32624614912263</v>
+        <v>2.978014999232427</v>
       </c>
       <c r="D10" t="n">
-        <v>18.22486991211506</v>
+        <v>2.961541360718698</v>
       </c>
       <c r="E10" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F10" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.786938604714849</v>
+        <v>0.940377523266163</v>
       </c>
       <c r="D11" t="n">
-        <v>3.876668583542026</v>
+        <v>0.6299586448255792</v>
       </c>
       <c r="E11" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F11" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.75162427360145</v>
+        <v>5.322138944460236</v>
       </c>
       <c r="D12" t="n">
-        <v>32.3413196823053</v>
+        <v>5.255464448374611</v>
       </c>
       <c r="E12" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F12" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.3533980362408</v>
+        <v>3.307427180889131</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6304310766888</v>
+        <v>3.02744504996193</v>
       </c>
       <c r="E13" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F13" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.83944745537565</v>
+        <v>5.823910211498543</v>
       </c>
       <c r="D14" t="n">
-        <v>35.17097563221639</v>
+        <v>5.715283540235164</v>
       </c>
       <c r="E14" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F14" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.45355819177839</v>
+        <v>2.186203206163988</v>
       </c>
       <c r="D15" t="n">
-        <v>15.22943888475148</v>
+        <v>2.474783818772116</v>
       </c>
       <c r="E15" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F15" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.43841480694616</v>
+        <v>2.833742406128752</v>
       </c>
       <c r="D16" t="n">
-        <v>17.70980479110277</v>
+        <v>2.8778432785542</v>
       </c>
       <c r="E16" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F16" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.92092770877953</v>
+        <v>4.212150752676674</v>
       </c>
       <c r="D17" t="n">
-        <v>26.4122317819597</v>
+        <v>4.291987664568452</v>
       </c>
       <c r="E17" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F17" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.75903127045362</v>
+        <v>3.698342581448713</v>
       </c>
       <c r="D18" t="n">
-        <v>24.7626911876947</v>
+        <v>4.02393731800039</v>
       </c>
       <c r="E18" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F18" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>32.73788242437048</v>
+        <v>5.319905893960202</v>
       </c>
       <c r="D19" t="n">
-        <v>19.87145926163753</v>
+        <v>3.229112130016099</v>
       </c>
       <c r="E19" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F19" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>6.602723950104135</v>
+        <v>1.072942641891922</v>
       </c>
       <c r="D20" t="n">
-        <v>5.729435177139789</v>
+        <v>0.9310332162852157</v>
       </c>
       <c r="E20" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F20" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>10.48991679952969</v>
+        <v>1.704611479923574</v>
       </c>
       <c r="D21" t="n">
-        <v>11.22447995670854</v>
+        <v>1.823977992965138</v>
       </c>
       <c r="E21" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F21" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>27.72617791590729</v>
+        <v>4.505503911334936</v>
       </c>
       <c r="D22" t="n">
-        <v>23.8142169782428</v>
+        <v>3.869810258964456</v>
       </c>
       <c r="E22" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F22" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.760753817841712</v>
+        <v>1.586122495399278</v>
       </c>
       <c r="D23" t="n">
-        <v>9.399152264576484</v>
+        <v>1.527362242993679</v>
       </c>
       <c r="E23" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F23" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>42.21677940551889</v>
+        <v>6.86022665339682</v>
       </c>
       <c r="D24" t="n">
-        <v>18.8837122980789</v>
+        <v>3.068603248437821</v>
       </c>
       <c r="E24" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F24" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>21.04686054605865</v>
+        <v>3.420114838734531</v>
       </c>
       <c r="D25" t="n">
-        <v>21.20038140999648</v>
+        <v>3.445061979124428</v>
       </c>
       <c r="E25" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F25" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>35.61539222860286</v>
+        <v>5.787501237147966</v>
       </c>
       <c r="D26" t="n">
-        <v>2.323074074896708</v>
+        <v>0.3774995371707152</v>
       </c>
       <c r="E26" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F26" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>27.92224671778761</v>
+        <v>4.537365091640487</v>
       </c>
       <c r="D27" t="n">
-        <v>27.62023356845149</v>
+        <v>4.488287954873367</v>
       </c>
       <c r="E27" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F27" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>49.85015520319963</v>
+        <v>8.10065022051994</v>
       </c>
       <c r="D28" t="n">
-        <v>13.52343171031644</v>
+        <v>2.197557652926422</v>
       </c>
       <c r="E28" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F28" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>37.56139079535059</v>
+        <v>6.103726004244471</v>
       </c>
       <c r="D29" t="n">
-        <v>16.94968811457139</v>
+        <v>2.754324318617851</v>
       </c>
       <c r="E29" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F29" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>27.03454066111379</v>
+        <v>4.393112857430991</v>
       </c>
       <c r="D30" t="n">
-        <v>28.31575113929724</v>
+        <v>4.601309560135802</v>
       </c>
       <c r="E30" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F30" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>44.14951819696196</v>
+        <v>7.174296707006319</v>
       </c>
       <c r="D31" t="n">
-        <v>19.5953675275677</v>
+        <v>3.184247223229751</v>
       </c>
       <c r="E31" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F31" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>51.88927356065572</v>
+        <v>8.432006953606555</v>
       </c>
       <c r="D32" t="n">
-        <v>25.3741095859142</v>
+        <v>4.123292807711058</v>
       </c>
       <c r="E32" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F32" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>15.95813474583285</v>
+        <v>2.593196896197838</v>
       </c>
       <c r="D33" t="n">
-        <v>16.18118863304333</v>
+        <v>2.629443152869541</v>
       </c>
       <c r="E33" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F33" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>3.494402455440865</v>
+        <v>0.5678403990091406</v>
       </c>
       <c r="D34" t="n">
-        <v>4.171247946643522</v>
+        <v>0.6778277913295724</v>
       </c>
       <c r="E34" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F34" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>24.87072154854379</v>
+        <v>4.041492251638366</v>
       </c>
       <c r="D35" t="n">
-        <v>23.53344065059607</v>
+        <v>3.824184105721861</v>
       </c>
       <c r="E35" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F35" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>6.730268076435738</v>
+        <v>1.093668562420808</v>
       </c>
       <c r="D36" t="n">
-        <v>4.988984502170472</v>
+        <v>0.8107099816027017</v>
       </c>
       <c r="E36" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F36" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>18.71474233881666</v>
+        <v>3.041145630057707</v>
       </c>
       <c r="D37" t="n">
-        <v>19.53171950943957</v>
+        <v>3.173904420283929</v>
       </c>
       <c r="E37" t="n">
-        <v>14.83785398917805</v>
+        <v>2.411151273241433</v>
       </c>
       <c r="F37" t="n">
-        <v>13.41444884454892</v>
+        <v>2.1798479372392</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
